--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D2">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E2">
         <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D3">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>426</v>
